--- a/03_Group_comparisons/Proteome_training/c_data/05_module_classification.xlsx
+++ b/03_Group_comparisons/Proteome_training/c_data/05_module_classification.xlsx
@@ -310,7 +310,7 @@
     <t>03_Group_comparisons/Proteome_training/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>614bbdf4f0c26542c91ed8556721be1c</t>
+    <t>2c8d64ee913e6b87df3bb15545693a35</t>
   </si>
   <si>
     <t>modules</t>
@@ -319,7 +319,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>BiocGenerics</t>
